--- a/examples/Apple DCF.xlsx
+++ b/examples/Apple DCF.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A513E1-A2C4-364F-938C-4055A04F6942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070D5DF8-7A68-864A-8A0C-4C4E879229B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="34200" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="34200" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DCF" sheetId="1" r:id="rId1"/>
@@ -84,9 +84,6 @@
     <t>Beta</t>
   </si>
   <si>
-    <t>Judgment: 5-year monthly regression against the S&amp;P 500 gives 1.10</t>
-  </si>
-  <si>
     <t>Equity risk premium</t>
   </si>
   <si>
@@ -313,6 +310,9 @@
   </si>
   <si>
     <t>Sources: Apple FY2025 Form 10-K and FY2026 10-Q filings via SEC EDGAR; analyst estimates and price from Yahoo Finance, 14 Oct 2026.</t>
+  </si>
+  <si>
+    <t>Judgment. 5-year monthly regression against the S&amp;P 500 gives 1.10. Blended toward 1: 0.67 × 1.10 + 0.33 = 1.07</t>
   </si>
 </sst>
 </file>
@@ -822,204 +822,204 @@
         <v>17</v>
       </c>
       <c r="C13" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="P13" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="9">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="P14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="7">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="10">
         <f>C12+C13*C14+C15</f>
-        <v>0.1014</v>
+        <v>0.10005</v>
       </c>
       <c r="P16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="7">
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="P17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" s="7">
         <v>0.21</v>
       </c>
       <c r="P18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" s="11">
         <f>C11/(C11+C7*C8)</f>
         <v>1.6571927729092266E-2</v>
       </c>
       <c r="P19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="12">
         <f>C16*(1-C19)+C17*(1-C18)*C19</f>
-        <v>0.10046584043391107</v>
+        <v>9.9138212536345346E-2</v>
       </c>
       <c r="P20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="9">
         <v>0.16</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="9">
         <v>0.01</v>
       </c>
       <c r="P22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="7">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="P23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="7">
         <v>0.3</v>
       </c>
       <c r="P24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="9">
         <v>0.32</v>
       </c>
       <c r="P25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="7">
         <v>0.16</v>
       </c>
       <c r="P26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.2">
       <c r="D30" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="F30" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="G30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="H30" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="I30" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="I30" s="13" t="s">
+      <c r="J30" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="K30" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K30" s="13" t="s">
+      <c r="L30" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="M30" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="M30" s="13" t="s">
+      <c r="N30" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="N30" s="13" t="s">
+      <c r="O30" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="O30" s="13" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E31" s="9">
         <v>0.12</v>
@@ -1056,12 +1056,12 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="P31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D32" s="6">
         <f>C9</f>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="11">
         <f>(29589+28202+32427+50852)/(95359+94036+102466+143756)</f>
@@ -1155,12 +1155,12 @@
         <v>0.32</v>
       </c>
       <c r="P33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E34" s="6">
         <f t="shared" ref="E34:O34" si="1">E32*E33</f>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E35" s="6">
         <f t="shared" ref="E35:N35" si="2">E34*(1-$C$21)</f>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E36" s="6">
         <f t="shared" ref="E36:N36" si="3">-E32*$C$22</f>
@@ -1305,12 +1305,12 @@
         <v>-17809.177222888655</v>
       </c>
       <c r="P36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E37" s="14">
         <f t="shared" ref="E37:O37" si="4">E35+E36</f>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E38" s="11">
         <f>(DATE(2026,12,31)-$C$6)/365</f>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E39" s="15">
         <f>E38/2</f>
@@ -1440,147 +1440,147 @@
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E40" s="16">
         <f t="shared" ref="E40:N40" si="5">1/(1+$C$20)^E39</f>
-        <v>0.98982307137476588</v>
+        <v>0.98995075030360069</v>
       </c>
       <c r="F40" s="16">
         <f t="shared" si="5"/>
-        <v>0.93395695742123275</v>
+        <v>0.93476194786867206</v>
       </c>
       <c r="G40" s="16">
         <f t="shared" si="5"/>
-        <v>0.84869236563760653</v>
+        <v>0.85044986809405665</v>
       </c>
       <c r="H40" s="16">
         <f t="shared" si="5"/>
-        <v>0.77121191267778844</v>
+        <v>0.77374242692516226</v>
       </c>
       <c r="I40" s="16">
         <f t="shared" si="5"/>
-        <v>0.70080495399448417</v>
+        <v>0.70395371400989926</v>
       </c>
       <c r="J40" s="16">
         <f t="shared" si="5"/>
-        <v>0.63682572256687076</v>
+        <v>0.6404596855799165</v>
       </c>
       <c r="K40" s="16">
         <f t="shared" si="5"/>
-        <v>0.57868740597688317</v>
+        <v>0.58269258431294724</v>
       </c>
       <c r="L40" s="16">
         <f t="shared" si="5"/>
-        <v>0.52585676421242489</v>
+        <v>0.53013586250298728</v>
       </c>
       <c r="M40" s="16">
         <f t="shared" si="5"/>
-        <v>0.47784923883242097</v>
+        <v>0.48231956314179852</v>
       </c>
       <c r="N40" s="16">
         <f t="shared" si="5"/>
-        <v>0.43422450863536666</v>
+        <v>0.43881611760982198</v>
       </c>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E41" s="14">
         <f t="shared" ref="E41:N41" si="6">E37*E38*E40</f>
-        <v>27575.195928626017</v>
+        <v>27578.752899139632</v>
       </c>
       <c r="F41" s="14">
         <f t="shared" si="6"/>
-        <v>134904.33900407964</v>
+        <v>135020.61492381393</v>
       </c>
       <c r="G41" s="14">
         <f t="shared" si="6"/>
-        <v>131169.58058184639</v>
+        <v>131441.21123320842</v>
       </c>
       <c r="H41" s="14">
         <f t="shared" si="6"/>
-        <v>126346.27110454798</v>
+        <v>126760.84073693668</v>
       </c>
       <c r="I41" s="14">
         <f t="shared" si="6"/>
-        <v>116762.39111239871</v>
+        <v>117287.01175947518</v>
       </c>
       <c r="J41" s="14">
         <f t="shared" si="6"/>
-        <v>111407.82945127814</v>
+        <v>112043.56371458304</v>
       </c>
       <c r="K41" s="14">
         <f t="shared" si="6"/>
-        <v>105286.45085761524</v>
+        <v>106015.15344851428</v>
       </c>
       <c r="L41" s="14">
         <f t="shared" si="6"/>
-        <v>99501.415553930448</v>
+        <v>100311.09675645913</v>
       </c>
       <c r="M41" s="14">
         <f t="shared" si="6"/>
-        <v>93130.067517714284</v>
+        <v>94001.308007236992</v>
       </c>
       <c r="N41" s="14">
         <f t="shared" si="6"/>
-        <v>87166.69433866578</v>
+        <v>88088.418856834585</v>
       </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D44" s="6">
         <f>SUM(E41:N41)</f>
-        <v>1033250.2354507025</v>
+        <v>1038547.9723362019</v>
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D45" s="6">
         <f>O37/(C20-C23)</f>
-        <v>2595889.0582201187</v>
+        <v>2642374.8664797815</v>
       </c>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D46" s="6">
         <f>D45/(1+C20)^(E38+9)</f>
-        <v>1074514.2445289341</v>
+        <v>1105989.1008361571</v>
       </c>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D47" s="14">
         <f>D44+D46</f>
-        <v>2107764.4799796366</v>
+        <v>2144537.0731723588</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D48" s="11">
         <f>D46/D47</f>
-        <v>0.50978857207960693</v>
+        <v>0.51572393626196245</v>
       </c>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D49" s="6">
         <f>C10</f>
@@ -1589,25 +1589,25 @@
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D50" s="14">
         <f>D47+D49</f>
-        <v>2169937.4799796366</v>
+        <v>2206710.0731723588</v>
       </c>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" s="17">
         <f>D50/C8</f>
-        <v>148.68492140573903</v>
+        <v>151.20459313784644</v>
       </c>
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D52" s="18">
         <f>C7</f>
@@ -1616,42 +1616,42 @@
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D53" s="19">
         <f>D51/D52-1</f>
-        <v>-0.56646570618807135</v>
+        <v>-0.55911886768764152</v>
       </c>
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D54" s="20">
         <f>C7/8.72</f>
         <v>39.330275229357795</v>
       </c>
       <c r="P54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D55" s="20">
         <f>D51/8.72</f>
-        <v>17.05102309698842</v>
+        <v>17.339976277275966</v>
       </c>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D59" s="21">
         <v>0.27</v>
@@ -1672,164 +1672,164 @@
     <row r="60" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C60" s="21">
         <f>$C$20+(-0.03)</f>
-        <v>7.0465840433911076E-2</v>
+        <v>6.9138212536345348E-2</v>
       </c>
       <c r="D60" s="18">
         <f t="shared" ref="D60:H64" si="7">(SUMPRODUCT($E$37:$H$37,$E$38:$H$38,1/(1+$C60)^$E$39:$H$39)+SUMPRODUCT($I$32:$N$32*($I$33:$N$33+D$59-$C$25)*(1-$C$21)+$I$36:$N$36,1/(1+$C60)^$I$39:$N$39)+$O$32*D$59*(1-$C$26)*(1-$C$23/$C$24)/($C60-$C$23)/(1+$C60)^($E$38+9)+$C$10)/$C$8</f>
-        <v>209.00294071040167</v>
+        <v>214.95759698416325</v>
       </c>
       <c r="E60" s="18">
         <f t="shared" si="7"/>
-        <v>225.35345339666245</v>
+        <v>231.85525476398874</v>
       </c>
       <c r="F60" s="18">
         <f t="shared" si="7"/>
-        <v>241.70396608292324</v>
+        <v>248.75291254381438</v>
       </c>
       <c r="G60" s="18">
         <f t="shared" si="7"/>
-        <v>258.05447876918402</v>
+        <v>265.6505703236399</v>
       </c>
       <c r="H60" s="18">
         <f t="shared" si="7"/>
-        <v>274.40499145544482</v>
+        <v>282.54822810346542</v>
       </c>
       <c r="P60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C61" s="21">
         <f>$C$20+(-0.015)</f>
-        <v>8.5465840433911075E-2</v>
+        <v>8.4138212536345347E-2</v>
       </c>
       <c r="D61" s="18">
         <f t="shared" si="7"/>
-        <v>159.9141553191059</v>
+        <v>163.25306292321304</v>
       </c>
       <c r="E61" s="18">
         <f t="shared" si="7"/>
-        <v>171.76639591355234</v>
+        <v>175.4103480939973</v>
       </c>
       <c r="F61" s="18">
         <f t="shared" si="7"/>
-        <v>183.61863650799879</v>
+        <v>187.56763326478159</v>
       </c>
       <c r="G61" s="18">
         <f t="shared" si="7"/>
-        <v>195.47087710244526</v>
+        <v>199.72491843556585</v>
       </c>
       <c r="H61" s="18">
         <f t="shared" si="7"/>
-        <v>207.3231176968917</v>
+        <v>211.88220360635012</v>
       </c>
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C62" s="21">
         <f>$C$20+(0)</f>
-        <v>0.10046584043391107</v>
+        <v>9.9138212536345346E-2</v>
       </c>
       <c r="D62" s="18">
         <f t="shared" si="7"/>
-        <v>130.36144803005834</v>
+        <v>132.49419251865095</v>
       </c>
       <c r="E62" s="18">
         <f t="shared" si="7"/>
-        <v>139.52318471789869</v>
+        <v>141.84939282824868</v>
       </c>
       <c r="F62" s="18">
         <f t="shared" si="7"/>
-        <v>148.68492140573903</v>
+        <v>151.20459313784644</v>
       </c>
       <c r="G62" s="18">
         <f t="shared" si="7"/>
-        <v>157.84665809357938</v>
+        <v>160.55979344744424</v>
       </c>
       <c r="H62" s="18">
         <f t="shared" si="7"/>
-        <v>167.00839478141967</v>
+        <v>169.914993757042</v>
       </c>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C63" s="21">
         <f>$C$20+(0.015)</f>
-        <v>0.11546584043391107</v>
+        <v>0.11413821253634535</v>
       </c>
       <c r="D63" s="18">
         <f t="shared" si="7"/>
-        <v>110.61677477993727</v>
+        <v>112.09619554901323</v>
       </c>
       <c r="E63" s="18">
         <f t="shared" si="7"/>
-        <v>117.9950110700418</v>
+        <v>119.60750461015571</v>
       </c>
       <c r="F63" s="18">
         <f t="shared" si="7"/>
-        <v>125.37324736014632</v>
+        <v>127.11881367129818</v>
       </c>
       <c r="G63" s="18">
         <f t="shared" si="7"/>
-        <v>132.75148365025089</v>
+        <v>134.63012273244067</v>
       </c>
       <c r="H63" s="18">
         <f t="shared" si="7"/>
-        <v>140.12971994035539</v>
+        <v>142.14143179358311</v>
       </c>
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C64" s="21">
         <f>$C$20+(0.03)</f>
-        <v>0.13046584043391107</v>
+        <v>0.12913821253634533</v>
       </c>
       <c r="D64" s="18">
         <f t="shared" si="7"/>
-        <v>96.488518902798049</v>
+        <v>97.574957425658212</v>
       </c>
       <c r="E64" s="18">
         <f t="shared" si="7"/>
-        <v>102.60213697046044</v>
+        <v>103.78536348265571</v>
       </c>
       <c r="F64" s="18">
         <f t="shared" si="7"/>
-        <v>108.71575503812282</v>
+        <v>109.99576953965322</v>
       </c>
       <c r="G64" s="18">
         <f t="shared" si="7"/>
-        <v>114.82937310578519</v>
+        <v>116.20617559665075</v>
       </c>
       <c r="H64" s="18">
         <f t="shared" si="7"/>
-        <v>120.94299117344757</v>
+        <v>122.41658165364824</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
